--- a/Documentacion Sprint (01 - 11)/Sprint 2 documentacion/Sprint_02_Backlog_ICARO.xlsx
+++ b/Documentacion Sprint (01 - 11)/Sprint 2 documentacion/Sprint_02_Backlog_ICARO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentos Base\Sprint 2 documentacion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentacion Sprint (01 - 11)\Sprint 2 documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC52E9B-802A-4A47-B586-10577BAA3A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1D3A6B-B901-4E2D-B5FF-DFCB5E7341A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5415" yWindow="1125" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Backlog Sprint 02" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="207">
   <si>
     <t>SPRINT BACKLOG — Sprint 02: Gestion de Proyectos, Avances de Obra y Evidencia Fotografica</t>
   </si>
@@ -451,9 +451,6 @@
     <t>Documento de resultados de pruebas del sprint</t>
   </si>
   <si>
-    <t>RESUMEN DE CASOS DE PRUEBA — SPRINT 07 (CP-123 a CP-168)</t>
-  </si>
-  <si>
     <t>ID CP</t>
   </si>
   <si>
@@ -641,13 +638,19 @@
   </si>
   <si>
     <t>proyectos_avances.test.js – Test 17</t>
+  </si>
+  <si>
+    <t>Los estados presentados en este documento corresponden al estado del Product/Sprint Backlog al cierre del Sprint respectivo. Debido a la naturaleza iterativa e incremental del proyecto, los elementos identificados como pendientes, diferidos o parcialmente implementados pudieron ser desarrollados y completados en sprints posteriores. Para conocer el estado definitivo de cada historia de usuario o historia técnica, debe consultarse el Product Backlog Consolidado al cierre del proyecto.</t>
+  </si>
+  <si>
+    <t>RESUMEN DE CASOS DE PRUEBA — SPRINT 02 (CP-016 a CP-032)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -741,8 +744,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -777,6 +787,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -858,10 +873,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -950,6 +966,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -986,7 +1005,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Neutral" xfId="1" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1287,7 +1307,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1304,124 +1324,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
     </row>
     <row r="3" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="38"/>
       <c r="G3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="35" t="s">
+      <c r="H3" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="38"/>
     </row>
     <row r="4" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="38">
+      <c r="B4" s="39">
         <v>46132</v>
       </c>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="41"/>
       <c r="G4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="38">
+      <c r="H4" s="39">
         <v>46136</v>
       </c>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="41"/>
     </row>
     <row r="5" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="38"/>
       <c r="G5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="35" t="s">
+      <c r="H5" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="37"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
+      <c r="L5" s="38"/>
     </row>
     <row r="6" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="37"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="38"/>
       <c r="G6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="35" t="s">
+      <c r="H6" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="37"/>
+      <c r="L6" s="38"/>
     </row>
     <row r="7" spans="1:12" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
@@ -1690,13 +1710,13 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
       <c r="F14" s="9">
         <v>34</v>
       </c>
@@ -1709,8 +1729,60 @@
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
     </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B16" s="31" t="s">
+        <v>205</v>
+      </c>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B17" s="31"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="31"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19" s="31"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="31"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
+    <mergeCell ref="B16:F22"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="B3:F3"/>
@@ -1738,12 +1810,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -1934,33 +2006,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
-        <v>142</v>
-      </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="A1" s="44" t="s">
+        <v>206</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="C2" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="D2" s="23" t="s">
         <v>145</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>146</v>
       </c>
       <c r="E2" s="23" t="s">
         <v>23</v>
       </c>
       <c r="F2" s="23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H2" s="29"/>
       <c r="I2" s="29"/>
@@ -1971,22 +2043,22 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="C3" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="D3" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="E3" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="C3" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="D3" s="25" t="s">
+      <c r="F3" s="25" t="s">
         <v>154</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="F3" s="25" t="s">
-        <v>155</v>
       </c>
       <c r="H3" s="30"/>
       <c r="I3" s="30"/>
@@ -1997,22 +2069,22 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="D4" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="E4" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="C4" s="27" t="s">
-        <v>153</v>
-      </c>
-      <c r="D4" s="28" t="s">
+      <c r="F4" s="28" t="s">
         <v>157</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="F4" s="28" t="s">
-        <v>158</v>
       </c>
       <c r="H4" s="30"/>
       <c r="I4" s="30"/>
@@ -2023,22 +2095,22 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="D5" s="25" t="s">
         <v>159</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="E5" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="C5" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="D5" s="25" t="s">
+      <c r="F5" s="25" t="s">
         <v>160</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="F5" s="25" t="s">
-        <v>161</v>
       </c>
       <c r="H5" s="30"/>
       <c r="I5" s="30"/>
@@ -2049,22 +2121,22 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="D6" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="E6" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="27" t="s">
-        <v>153</v>
-      </c>
-      <c r="D6" s="28" t="s">
+      <c r="F6" s="28" t="s">
         <v>163</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>164</v>
       </c>
       <c r="H6" s="30"/>
       <c r="I6" s="30"/>
@@ -2075,22 +2147,22 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" s="25" t="s">
         <v>165</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="E7" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="C7" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="D7" s="25" t="s">
+      <c r="F7" s="25" t="s">
         <v>166</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="F7" s="25" t="s">
-        <v>167</v>
       </c>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
@@ -2101,22 +2173,22 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="D8" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="E8" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="C8" s="27" t="s">
-        <v>153</v>
-      </c>
-      <c r="D8" s="28" t="s">
+      <c r="F8" s="28" t="s">
         <v>169</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="F8" s="28" t="s">
-        <v>170</v>
       </c>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
@@ -2127,22 +2199,22 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="D9" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="E9" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="C9" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="D9" s="25" t="s">
+      <c r="F9" s="25" t="s">
         <v>172</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="F9" s="25" t="s">
-        <v>173</v>
       </c>
       <c r="H9" s="30"/>
       <c r="I9" s="30"/>
@@ -2153,22 +2225,22 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" s="27" t="s">
         <v>174</v>
       </c>
-      <c r="B10" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="C10" s="27" t="s">
+      <c r="D10" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="E10" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="F10" s="28" t="s">
         <v>176</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="F10" s="28" t="s">
-        <v>177</v>
       </c>
       <c r="H10" s="30"/>
       <c r="I10" s="30"/>
@@ -2179,22 +2251,22 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="D11" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="B11" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="D11" s="25" t="s">
+      <c r="E11" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="F11" s="25" t="s">
         <v>179</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="F11" s="25" t="s">
-        <v>180</v>
       </c>
       <c r="H11" s="30"/>
       <c r="I11" s="30"/>
@@ -2205,22 +2277,22 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="27" t="s">
+        <v>180</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="D12" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="B12" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="D12" s="28" t="s">
+      <c r="E12" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="F12" s="28" t="s">
         <v>182</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="F12" s="28" t="s">
-        <v>183</v>
       </c>
       <c r="H12" s="30"/>
       <c r="I12" s="30"/>
@@ -2231,22 +2303,22 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="D13" s="25" t="s">
         <v>184</v>
       </c>
-      <c r="B13" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="D13" s="25" t="s">
+      <c r="E13" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="F13" s="25" t="s">
         <v>185</v>
-      </c>
-      <c r="E13" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="F13" s="25" t="s">
-        <v>186</v>
       </c>
       <c r="H13" s="30"/>
       <c r="I13" s="30"/>
@@ -2257,22 +2329,22 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="D14" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="B14" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="C14" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="D14" s="28" t="s">
+      <c r="E14" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="F14" s="28" t="s">
         <v>188</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="F14" s="28" t="s">
-        <v>189</v>
       </c>
       <c r="H14" s="30"/>
       <c r="I14" s="30"/>
@@ -2283,22 +2355,22 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="D15" s="25" t="s">
         <v>190</v>
       </c>
-      <c r="B15" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="D15" s="25" t="s">
+      <c r="E15" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="F15" s="25" t="s">
         <v>191</v>
-      </c>
-      <c r="E15" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="F15" s="25" t="s">
-        <v>192</v>
       </c>
       <c r="H15" s="30"/>
       <c r="I15" s="30"/>
@@ -2309,22 +2381,22 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="D16" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="B16" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="C16" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="D16" s="28" t="s">
+      <c r="E16" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="F16" s="28" t="s">
         <v>194</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="F16" s="28" t="s">
-        <v>195</v>
       </c>
       <c r="H16" s="30"/>
       <c r="I16" s="30"/>
@@ -2335,22 +2407,22 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
+        <v>195</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="C17" s="24" t="s">
         <v>196</v>
       </c>
-      <c r="B17" s="24" t="s">
-        <v>151</v>
-      </c>
-      <c r="C17" s="24" t="s">
+      <c r="D17" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="D17" s="25" t="s">
+      <c r="E17" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="F17" s="25" t="s">
         <v>198</v>
-      </c>
-      <c r="E17" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="F17" s="25" t="s">
-        <v>199</v>
       </c>
       <c r="H17" s="30"/>
       <c r="I17" s="30"/>
@@ -2361,22 +2433,22 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="D18" s="28" t="s">
         <v>200</v>
       </c>
-      <c r="B18" s="27" t="s">
-        <v>151</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="D18" s="28" t="s">
+      <c r="E18" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="F18" s="28" t="s">
         <v>201</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="F18" s="28" t="s">
-        <v>202</v>
       </c>
       <c r="H18" s="30"/>
       <c r="I18" s="30"/>
@@ -2387,22 +2459,22 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="D19" s="25" t="s">
         <v>203</v>
       </c>
-      <c r="B19" s="24" t="s">
-        <v>151</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="D19" s="25" t="s">
+      <c r="E19" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="F19" s="25" t="s">
         <v>204</v>
-      </c>
-      <c r="E19" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="F19" s="25" t="s">
-        <v>205</v>
       </c>
       <c r="H19" s="30"/>
       <c r="I19" s="30"/>
@@ -2429,11 +2501,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="45" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
